--- a/artfynd/A 50052-2025 artfynd.xlsx
+++ b/artfynd/A 50052-2025 artfynd.xlsx
@@ -949,7 +949,7 @@
         <v>93734240</v>
       </c>
       <c r="B4" t="n">
-        <v>100851</v>
+        <v>100856</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50052-2025 artfynd.xlsx
+++ b/artfynd/A 50052-2025 artfynd.xlsx
@@ -949,7 +949,7 @@
         <v>93734240</v>
       </c>
       <c r="B4" t="n">
-        <v>100856</v>
+        <v>100864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50052-2025 artfynd.xlsx
+++ b/artfynd/A 50052-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>526338</v>
       </c>
       <c r="B2" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619918.4339556777</v>
+        <v>619918</v>
       </c>
       <c r="R2" t="n">
-        <v>6740664.42217462</v>
+        <v>6740664</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +757,9 @@
           <t>2012-11-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-11-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65082155</v>
+        <v>65082150</v>
       </c>
       <c r="B3" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619916.5763637346</v>
+        <v>619917</v>
       </c>
       <c r="R3" t="n">
-        <v>6740661.427354161</v>
+        <v>6740661</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,27 +875,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-04-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-04-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>en tuva med 3 blommor och 7 rosetter. Inventerad av Gunnar Bakken.</t>
+          <t>kontroll lokal 80. en tuva med 2 blommor, 4 rosett. blommor knäckta under 1/2 m avverkningsrester och skogsmaskiner. Inventerad av Gunnar Bakken.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -949,7 +919,7 @@
         <v>93734240</v>
       </c>
       <c r="B4" t="n">
-        <v>100864</v>
+        <v>101345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50052-2025 artfynd.xlsx
+++ b/artfynd/A 50052-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/526338</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65082150</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,8 +1044,18 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93734240</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>